--- a/GHG_Calculation/output/continent_result.xlsx
+++ b/GHG_Calculation/output/continent_result.xlsx
@@ -496,12 +496,12 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CH4_Indensity</t>
+          <t>CH4_Intensity</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>N2O_Indensity</t>
+          <t>N2O_Intensity</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.089287429265887</v>
+        <v>9.047221198036846</v>
       </c>
       <c r="C2" t="n">
         <v>6.080525240281475</v>
@@ -546,25 +546,25 @@
         <v>6.118951014001717</v>
       </c>
       <c r="E2" t="n">
-        <v>3.989784006564775</v>
+        <v>3.992447099351615</v>
       </c>
       <c r="F2" t="n">
-        <v>25.27854769011385</v>
+        <v>25.15543585712123</v>
       </c>
       <c r="G2" t="n">
-        <v>10.52729436009094</v>
+        <v>10.48238487605458</v>
       </c>
       <c r="H2" t="n">
         <v>0.2005353873705443</v>
       </c>
       <c r="I2" t="n">
-        <v>4.176362447433274</v>
+        <v>4.185487920674468</v>
       </c>
       <c r="J2" t="n">
-        <v>14.90419219489477</v>
+        <v>14.86840818409959</v>
       </c>
       <c r="K2" t="n">
-        <v>19.61658178935683</v>
+        <v>19.52960607409142</v>
       </c>
       <c r="L2" t="n">
         <v>602645049.2209216</v>
@@ -573,10 +573,10 @@
         <v>20028411285437.27</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02501616543695475</v>
+        <v>0.02453478246603405</v>
       </c>
       <c r="O2" t="n">
-        <v>0.606765452866593</v>
+        <v>0.604260045353197</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>16.65178058015516</v>
+        <v>16.62922009974995</v>
       </c>
       <c r="R2" t="n">
-        <v>17.18036475355579</v>
+        <v>17.21821168619859</v>
       </c>
       <c r="S2" t="n">
-        <v>16.22088755923412</v>
+        <v>16.15233743648541</v>
       </c>
       <c r="T2" t="n">
         <v>7.552502334730457</v>
@@ -603,34 +603,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.238017673619495</v>
+        <v>2.262810416964417</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9714699647984916</v>
+        <v>0.8886646140265873</v>
       </c>
       <c r="D3" t="n">
         <v>1.748381795510944</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8869566580504616</v>
+        <v>0.8875340040613026</v>
       </c>
       <c r="F3" t="n">
-        <v>5.844826091979391</v>
+        <v>5.579030243458922</v>
       </c>
       <c r="G3" t="n">
-        <v>3.17299993464146</v>
+        <v>3.176115709493525</v>
       </c>
       <c r="H3" t="n">
         <v>0.09402759425994424</v>
       </c>
       <c r="I3" t="n">
-        <v>1.486516030853155</v>
+        <v>1.489208840899658</v>
       </c>
       <c r="J3" t="n">
-        <v>4.753543559754558</v>
+        <v>4.759352144653128</v>
       </c>
       <c r="K3" t="n">
-        <v>5.411017608260954</v>
+        <v>5.438926126457941</v>
       </c>
       <c r="L3" t="n">
         <v>213851293.529946</v>
@@ -639,10 +639,10 @@
         <v>8249712267006.462</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01709913424581881</v>
+        <v>0.01669792021591355</v>
       </c>
       <c r="O3" t="n">
-        <v>0.510311488402477</v>
+        <v>0.5101817772040018</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>4.593209912697618</v>
+        <v>4.631178904480659</v>
       </c>
       <c r="R3" t="n">
-        <v>4.230250199139403</v>
+        <v>4.306465810019422</v>
       </c>
       <c r="S3" t="n">
-        <v>4.889088630445753</v>
+        <v>4.894085962656517</v>
       </c>
       <c r="T3" t="n">
         <v>2.680039263174909</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.230830639773457</v>
+        <v>3.22326846910508</v>
       </c>
       <c r="C4" t="n">
         <v>2.714059587208246</v>
@@ -678,25 +678,25 @@
         <v>9.617354451664649</v>
       </c>
       <c r="E4" t="n">
-        <v>3.886306481613898</v>
+        <v>3.889112934058814</v>
       </c>
       <c r="F4" t="n">
-        <v>19.44855116026025</v>
+        <v>19.08822664799152</v>
       </c>
       <c r="G4" t="n">
-        <v>2.131408095341623</v>
+        <v>2.107171761199825</v>
       </c>
       <c r="H4" t="n">
         <v>0.3733619809327932</v>
       </c>
       <c r="I4" t="n">
-        <v>4.557597406458257</v>
+        <v>4.569736607737672</v>
       </c>
       <c r="J4" t="n">
-        <v>7.062367482732672</v>
+        <v>7.050270349870291</v>
       </c>
       <c r="K4" t="n">
-        <v>5.36223873511508</v>
+        <v>5.330440230304904</v>
       </c>
       <c r="L4" t="n">
         <v>434353764.87612</v>
@@ -705,10 +705,10 @@
         <v>6435782653182.117</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04239213417182214</v>
+        <v>0.04084040719470577</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4032720856393438</v>
+        <v>0.3993156929644049</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>4.551803356688302</v>
+        <v>4.538804494162124</v>
       </c>
       <c r="R4" t="n">
-        <v>6.106842728897519</v>
+        <v>6.13436077306734</v>
       </c>
       <c r="S4" t="n">
-        <v>3.284161141009374</v>
+        <v>3.246947114228017</v>
       </c>
       <c r="T4" t="n">
         <v>5.443432792763701</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.107879761411508</v>
+        <v>6.934583850676816</v>
       </c>
       <c r="C5" t="n">
         <v>6.621137580208027</v>
@@ -744,25 +744,25 @@
         <v>9.49777040673732</v>
       </c>
       <c r="E5" t="n">
-        <v>6.659826781146402</v>
+        <v>6.664634142968835</v>
       </c>
       <c r="F5" t="n">
-        <v>29.88661452950326</v>
+        <v>29.29127789278538</v>
       </c>
       <c r="G5" t="n">
-        <v>5.953001237140517</v>
+        <v>5.93688217381227</v>
       </c>
       <c r="H5" t="n">
         <v>0.5111792005071126</v>
       </c>
       <c r="I5" t="n">
-        <v>8.755434316547543</v>
+        <v>8.778511209987697</v>
       </c>
       <c r="J5" t="n">
-        <v>15.21961475419517</v>
+        <v>15.22657258430708</v>
       </c>
       <c r="K5" t="n">
-        <v>13.06088099855203</v>
+        <v>12.87146602448909</v>
       </c>
       <c r="L5" t="n">
         <v>864709440.5918708</v>
@@ -771,10 +771,10 @@
         <v>15097573822030.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04681299218106177</v>
+        <v>0.04586520326816472</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5071370481959799</v>
+        <v>0.5056939936618295</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>11.08689204402603</v>
+        <v>10.95989548973227</v>
       </c>
       <c r="R5" t="n">
-        <v>13.4351529617465</v>
+        <v>13.19754763181389</v>
       </c>
       <c r="S5" t="n">
-        <v>9.172628826045646</v>
+        <v>9.148159061696672</v>
       </c>
       <c r="T5" t="n">
         <v>10.83676050666351</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.96581136095081</v>
+        <v>12.88759945680162</v>
       </c>
       <c r="C6" t="n">
         <v>4.467766804475843</v>
@@ -810,25 +810,25 @@
         <v>14.20778343736278</v>
       </c>
       <c r="E6" t="n">
-        <v>4.98285263067329</v>
+        <v>4.983268031233171</v>
       </c>
       <c r="F6" t="n">
-        <v>36.62421423346272</v>
+        <v>34.60790652262799</v>
       </c>
       <c r="G6" t="n">
-        <v>7.761492289742717</v>
+        <v>7.749628723593153</v>
       </c>
       <c r="H6" t="n">
         <v>0.2976130626613852</v>
       </c>
       <c r="I6" t="n">
-        <v>5.767052306892655</v>
+        <v>5.768354879274928</v>
       </c>
       <c r="J6" t="n">
-        <v>13.82615765929676</v>
+        <v>13.81559666552947</v>
       </c>
       <c r="K6" t="n">
-        <v>20.72730365069352</v>
+        <v>20.63722818039477</v>
       </c>
       <c r="L6" t="n">
         <v>647317795.9752181</v>
@@ -837,10 +837,10 @@
         <v>24012265070795.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03513065626833293</v>
+        <v>0.03413151452573521</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4216820684068176</v>
+        <v>0.422881039014188</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>17.59463071170025</v>
+        <v>17.57234674158745</v>
       </c>
       <c r="R6" t="n">
-        <v>24.50768228427824</v>
+        <v>24.5270244550115</v>
       </c>
       <c r="S6" t="n">
-        <v>11.95922612376648</v>
+        <v>11.94142550870259</v>
       </c>
       <c r="T6" t="n">
         <v>8.112352655573236</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.80034584050661</v>
+        <v>15.76139298494375</v>
       </c>
       <c r="C7" t="n">
         <v>11.7525366653122</v>
@@ -876,25 +876,25 @@
         <v>135.884313344889</v>
       </c>
       <c r="E7" t="n">
-        <v>10.60211252361994</v>
+        <v>10.60536173749433</v>
       </c>
       <c r="F7" t="n">
-        <v>174.0393083743277</v>
+        <v>159.5724801819868</v>
       </c>
       <c r="G7" t="n">
-        <v>33.53132240494877</v>
+        <v>33.60362836418216</v>
       </c>
       <c r="H7" t="n">
         <v>7.583437662630718</v>
       </c>
       <c r="I7" t="n">
-        <v>28.66421437800658</v>
+        <v>28.67896940518972</v>
       </c>
       <c r="J7" t="n">
-        <v>69.77897444558606</v>
+        <v>69.86603543200259</v>
       </c>
       <c r="K7" t="n">
-        <v>49.33166824545538</v>
+        <v>49.36502134912592</v>
       </c>
       <c r="L7" t="n">
         <v>4003531527.863863</v>
@@ -903,10 +903,10 @@
         <v>34059927035882.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04800714570898228</v>
+        <v>0.04790110351062832</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6573291431544642</v>
+        <v>0.6572688937302785</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>41.87580303730704</v>
+        <v>42.03371036410734</v>
       </c>
       <c r="R7" t="n">
-        <v>29.86545500785821</v>
+        <v>29.99628227759197</v>
       </c>
       <c r="S7" t="n">
-        <v>51.66643886249259</v>
+        <v>51.77992898051424</v>
       </c>
       <c r="T7" t="n">
         <v>50.17328400929825</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.472917259949803</v>
+        <v>2.427611767317009</v>
       </c>
       <c r="C8" t="n">
         <v>1.18381689120968</v>
@@ -942,25 +942,25 @@
         <v>39.03319042708687</v>
       </c>
       <c r="E8" t="n">
-        <v>1.927667227039267</v>
+        <v>1.928578325231786</v>
       </c>
       <c r="F8" t="n">
-        <v>44.61759180528561</v>
+        <v>37.78804449228807</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82210151485214</v>
+        <v>1.841203559120276</v>
       </c>
       <c r="H8" t="n">
         <v>0.8595121501418735</v>
       </c>
       <c r="I8" t="n">
-        <v>9.167542006963075</v>
+        <v>9.171137441365815</v>
       </c>
       <c r="J8" t="n">
-        <v>11.84915567195709</v>
+        <v>11.87185315062796</v>
       </c>
       <c r="K8" t="n">
-        <v>4.295018774801943</v>
+        <v>4.268815326437284</v>
       </c>
       <c r="L8" t="n">
         <v>1213000104.085456</v>
@@ -969,10 +969,10 @@
         <v>4222048019689.039</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04507534005359983</v>
+        <v>0.04446688629135639</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5039748290438572</v>
+        <v>0.5087490309567299</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3.6458803574256</v>
+        <v>3.634843906180226</v>
       </c>
       <c r="R8" t="n">
-        <v>4.674252064524357</v>
+        <v>4.62010736629728</v>
       </c>
       <c r="S8" t="n">
-        <v>2.807568857006045</v>
+        <v>2.837115935716551</v>
       </c>
       <c r="T8" t="n">
         <v>15.20162843779594</v>
